--- a/files/Financial_Performance_Dashboard.xlsx
+++ b/files/Financial_Performance_Dashboard.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kieranoconnell/Desktop/portfolio - Main/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D146B-6260-024F-8DE2-E0D76D190F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F293E8-E601-104A-8488-726117B70205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38380" yWindow="-1360" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{96DCEB71-72FD-9843-90E9-7993DCC534D5}"/>
+    <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{96DCEB71-72FD-9843-90E9-7993DCC534D5}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Raw_Data(apple)" sheetId="8" r:id="rId2"/>
+    <sheet name="Raw_Data" sheetId="8" r:id="rId2"/>
     <sheet name="Clean_Data" sheetId="9" r:id="rId3"/>
     <sheet name="Pivot_Tables" sheetId="11" r:id="rId4"/>
     <sheet name="Dashboard" sheetId="6" r:id="rId5"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -119,12 +119,6 @@
     <t>Net Margin</t>
   </si>
   <si>
-    <t>Apple SE: Raw Data $ In Millions</t>
-  </si>
-  <si>
-    <t>Apple Debt: Raw Data $ In Millions</t>
-  </si>
-  <si>
     <t>ROE</t>
   </si>
   <si>
@@ -195,6 +189,12 @@
   </si>
   <si>
     <t>I t</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SE: Raw Data $ In Millions</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Debt: Raw Data $ In Millions</t>
   </si>
 </sst>
 </file>
@@ -1853,7 +1853,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-72DC-9D40-B791-4C76486614D3}"/>
+              <c16:uniqueId val="{00000001-2A17-914B-A20B-D23944061DC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2869,7 +2869,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-4C74-C344-916C-A63D7336DAA4}"/>
+              <c16:uniqueId val="{00000001-5A1F-E34B-B727-9B08799F71D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4151,7 +4151,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-9612-2047-9E01-38493E4E9616}"/>
+              <c16:uniqueId val="{00000001-BD35-8C4C-83BD-866DA7455E55}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5117,7 +5117,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-02FA-744A-8CB5-FD61015ED30B}"/>
+              <c16:uniqueId val="{00000001-7215-2649-8ECF-EDC5B4956B07}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7524,8 +7524,8 @@
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7541,7 +7541,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="25400"/>
-          <a:ext cx="14135100" cy="7251700"/>
+          <a:ext cx="14135100" cy="7645400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7587,6 +7587,18 @@
             <a:rPr lang="en-CA" sz="1600"/>
             <a:t>By: Kieran O'Connell | Finance Student</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600"/>
+            <a:t>March 22,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600" baseline="0"/>
+            <a:t> 2026</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-CA" sz="1600"/>
         </a:p>
         <a:p>
           <a:endParaRPr lang="en-CA" sz="1600"/>
@@ -8993,7 +9005,168 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0BE29C4-E316-5D4B-A04F-4340FF62A023}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78E518E5-BE24-F74E-A6D9-9691F0663DBB}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A10:D27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item m="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Revenue Comparison (Apple Vs. Microsoft)" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="2" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0BE29C4-E316-5D4B-A04F-4340FF62A023}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="F29:I46" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisCol" showAll="0">
@@ -9153,8 +9326,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7BAF44B1-D182-7A49-BEBD-81A7A91DB500}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7BAF44B1-D182-7A49-BEBD-81A7A91DB500}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="F10:I27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisCol" showAll="0">
@@ -9314,8 +9487,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AE4D390-E515-F74E-8979-DCC5BD8858AA}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7AE4D390-E515-F74E-8979-DCC5BD8858AA}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A29:D46" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisCol" showAll="0">
@@ -9454,167 +9627,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="4" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78E518E5-BE24-F74E-A6D9-9691F0663DBB}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A10:D27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item m="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="16">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Revenue Comparison (Apple Vs. Microsoft)" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="2" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="8" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -10140,28 +10152,28 @@
   <sheetData>
     <row r="1" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" s="36"/>
       <c r="E1" s="36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F1" s="36"/>
       <c r="G1" s="36"/>
       <c r="I1" s="36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J1" s="36"/>
       <c r="K1" s="36"/>
       <c r="M1" s="36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N1" s="36"/>
       <c r="O1" s="36"/>
     </row>
     <row r="2" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1</v>
@@ -10171,7 +10183,7 @@
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>1</v>
@@ -10180,7 +10192,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>1</v>
@@ -10189,7 +10201,7 @@
         <v>8</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N2" s="14" t="s">
         <v>1</v>
@@ -10200,7 +10212,7 @@
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8">
         <v>2025</v>
@@ -10210,7 +10222,7 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" s="8">
         <v>2025</v>
@@ -10219,7 +10231,7 @@
         <v>112010</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J3" s="8">
         <v>2025</v>
@@ -10228,7 +10240,7 @@
         <v>98767</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N3" s="8">
         <v>2025</v>
@@ -10239,7 +10251,7 @@
     </row>
     <row r="4" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="8">
         <v>2024</v>
@@ -10249,7 +10261,7 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" s="8">
         <v>2024</v>
@@ -10258,7 +10270,7 @@
         <v>93736</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="8">
         <v>2024</v>
@@ -10267,7 +10279,7 @@
         <v>108807</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N4" s="8">
         <v>2024</v>
@@ -10278,7 +10290,7 @@
     </row>
     <row r="5" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8">
         <v>2023</v>
@@ -10288,7 +10300,7 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" s="8">
         <v>2023</v>
@@ -10297,7 +10309,7 @@
         <v>96995</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5" s="8">
         <v>2023</v>
@@ -10306,7 +10318,7 @@
         <v>99584</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N5" s="8">
         <v>2023</v>
@@ -10317,7 +10329,7 @@
     </row>
     <row r="6" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" s="8">
         <v>2022</v>
@@ -10327,7 +10339,7 @@
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" s="8">
         <v>2022</v>
@@ -10336,7 +10348,7 @@
         <v>99803</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J6" s="8">
         <v>2022</v>
@@ -10345,7 +10357,7 @@
         <v>111443</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N6" s="8">
         <v>2022</v>
@@ -10356,7 +10368,7 @@
     </row>
     <row r="7" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>2021</v>
@@ -10366,7 +10378,7 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="8">
         <v>2021</v>
@@ -10375,7 +10387,7 @@
         <v>94680</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J7" s="8">
         <v>2021</v>
@@ -10384,7 +10396,7 @@
         <v>92953</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N7" s="8">
         <v>2021</v>
@@ -10395,7 +10407,7 @@
     </row>
     <row r="8" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8">
         <v>2020</v>
@@ -10405,7 +10417,7 @@
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" s="8">
         <v>2020</v>
@@ -10414,7 +10426,7 @@
         <v>57411</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J8" s="8">
         <v>2020</v>
@@ -10423,7 +10435,7 @@
         <v>73365</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N8" s="8">
         <v>2020</v>
@@ -10434,7 +10446,7 @@
     </row>
     <row r="9" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8">
         <v>2019</v>
@@ -10444,7 +10456,7 @@
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8">
         <v>2019</v>
@@ -10453,7 +10465,7 @@
         <v>55256</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J9" s="8">
         <v>2019</v>
@@ -10462,7 +10474,7 @@
         <v>58896</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N9" s="8">
         <v>2019</v>
@@ -10473,7 +10485,7 @@
     </row>
     <row r="10" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" s="8">
         <v>2018</v>
@@ -10483,7 +10495,7 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" s="8">
         <v>2018</v>
@@ -10492,7 +10504,7 @@
         <v>59531</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J10" s="8">
         <v>2018</v>
@@ -10501,7 +10513,7 @@
         <v>64121</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N10" s="8">
         <v>2018</v>
@@ -10512,7 +10524,7 @@
     </row>
     <row r="11" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" s="8">
         <v>2017</v>
@@ -10522,7 +10534,7 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" s="8">
         <v>2017</v>
@@ -10531,7 +10543,7 @@
         <v>48351</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J11" s="8">
         <v>2017</v>
@@ -10540,7 +10552,7 @@
         <v>51774</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N11" s="8">
         <v>2017</v>
@@ -10551,7 +10563,7 @@
     </row>
     <row r="12" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="8">
         <v>2016</v>
@@ -10561,7 +10573,7 @@
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" s="8">
         <v>2016</v>
@@ -10570,7 +10582,7 @@
         <v>45687</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J12" s="8">
         <v>2016</v>
@@ -10579,7 +10591,7 @@
         <v>53497</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N12" s="8">
         <v>2016</v>
@@ -10590,7 +10602,7 @@
     </row>
     <row r="13" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8">
         <v>2015</v>
@@ -10600,7 +10612,7 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" s="8">
         <v>2015</v>
@@ -10609,7 +10621,7 @@
         <v>53394</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J13" s="8">
         <v>2015</v>
@@ -10618,7 +10630,7 @@
         <v>70019</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N13" s="8">
         <v>2015</v>
@@ -10629,7 +10641,7 @@
     </row>
     <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="8">
         <v>2014</v>
@@ -10639,7 +10651,7 @@
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" s="8">
         <v>2014</v>
@@ -10648,7 +10660,7 @@
         <v>39510</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J14" s="8">
         <v>2014</v>
@@ -10657,7 +10669,7 @@
         <v>50142</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N14" s="8">
         <v>2014</v>
@@ -10668,7 +10680,7 @@
     </row>
     <row r="15" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="8">
         <v>2013</v>
@@ -10678,7 +10690,7 @@
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" s="8">
         <v>2013</v>
@@ -10687,7 +10699,7 @@
         <v>37037</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" s="8">
         <v>2013</v>
@@ -10696,7 +10708,7 @@
         <v>45501</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N15" s="8">
         <v>2013</v>
@@ -10707,7 +10719,7 @@
     </row>
     <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="8">
         <v>2012</v>
@@ -10717,7 +10729,7 @@
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" s="8">
         <v>2012</v>
@@ -10726,7 +10738,7 @@
         <v>41733</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J16" s="8">
         <v>2012</v>
@@ -10735,7 +10747,7 @@
         <v>42561</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N16" s="8">
         <v>2012</v>
@@ -10746,7 +10758,7 @@
     </row>
     <row r="17" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8">
         <v>2011</v>
@@ -10756,7 +10768,7 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" s="8">
         <v>2011</v>
@@ -10765,7 +10777,7 @@
         <v>25922</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J17" s="8">
         <v>2011</v>
@@ -10774,7 +10786,7 @@
         <v>33269</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N17" s="8">
         <v>2011</v>
@@ -10785,7 +10797,7 @@
     </row>
     <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="9">
         <v>2025</v>
@@ -10795,7 +10807,7 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F18" s="8">
         <v>2025</v>
@@ -10804,7 +10816,7 @@
         <v>101832</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J18" s="8">
         <v>2025</v>
@@ -10813,7 +10825,7 @@
         <v>71611</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N18" s="8">
         <v>2025</v>
@@ -10824,7 +10836,7 @@
     </row>
     <row r="19" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="9">
         <v>2024</v>
@@ -10834,7 +10846,7 @@
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F19" s="8">
         <v>2024</v>
@@ -10843,7 +10855,7 @@
         <v>88136</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J19" s="8">
         <v>2024</v>
@@ -10852,7 +10864,7 @@
         <v>74071</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N19" s="8">
         <v>2024</v>
@@ -10863,7 +10875,7 @@
     </row>
     <row r="20" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="9">
         <v>2023</v>
@@ -10873,7 +10885,7 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F20" s="8">
         <v>2023</v>
@@ -10882,7 +10894,7 @@
         <v>72361</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J20" s="8">
         <v>2023</v>
@@ -10891,7 +10903,7 @@
         <v>59475</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N20" s="8">
         <v>2023</v>
@@ -10902,7 +10914,7 @@
     </row>
     <row r="21" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" s="9">
         <v>2022</v>
@@ -10912,7 +10924,7 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F21" s="8">
         <v>2022</v>
@@ -10921,7 +10933,7 @@
         <v>72738</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J21" s="8">
         <v>2022</v>
@@ -10930,7 +10942,7 @@
         <v>65149</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N21" s="8">
         <v>2022</v>
@@ -10941,7 +10953,7 @@
     </row>
     <row r="22" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="9">
         <v>2021</v>
@@ -10951,7 +10963,7 @@
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F22" s="8">
         <v>2021</v>
@@ -10960,7 +10972,7 @@
         <v>61271</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J22" s="8">
         <v>2021</v>
@@ -10969,7 +10981,7 @@
         <v>56118</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N22" s="8">
         <v>2021</v>
@@ -10980,7 +10992,7 @@
     </row>
     <row r="23" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23" s="9">
         <v>2020</v>
@@ -10990,7 +11002,7 @@
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F23" s="8">
         <v>2020</v>
@@ -10999,7 +11011,7 @@
         <v>44281</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J23" s="8">
         <v>2020</v>
@@ -11008,7 +11020,7 @@
         <v>45234</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N23" s="8">
         <v>2020</v>
@@ -11019,7 +11031,7 @@
     </row>
     <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="9">
         <v>2019</v>
@@ -11029,7 +11041,7 @@
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F24" s="8">
         <v>2019</v>
@@ -11038,7 +11050,7 @@
         <v>39240</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J24" s="8">
         <v>2019</v>
@@ -11047,7 +11059,7 @@
         <v>38260</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N24" s="8">
         <v>2019</v>
@@ -11058,7 +11070,7 @@
     </row>
     <row r="25" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B25" s="9">
         <v>2018</v>
@@ -11068,7 +11080,7 @@
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F25" s="8">
         <v>2018</v>
@@ -11077,7 +11089,7 @@
         <v>16571</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J25" s="8">
         <v>2018</v>
@@ -11086,7 +11098,7 @@
         <v>32353</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N25" s="8">
         <v>2018</v>
@@ -11097,7 +11109,7 @@
     </row>
     <row r="26" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26" s="9">
         <v>2017</v>
@@ -11107,7 +11119,7 @@
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F26" s="8">
         <v>2017</v>
@@ -11116,7 +11128,7 @@
         <v>25489</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J26" s="8">
         <v>2017</v>
@@ -11125,7 +11137,7 @@
         <v>31378</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N26" s="8">
         <v>2017</v>
@@ -11136,7 +11148,7 @@
     </row>
     <row r="27" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" s="9">
         <v>2016</v>
@@ -11146,7 +11158,7 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F27" s="8">
         <v>2016</v>
@@ -11155,7 +11167,7 @@
         <v>20539</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J27" s="8">
         <v>2016</v>
@@ -11164,7 +11176,7 @@
         <v>24928</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N27" s="8">
         <v>2016</v>
@@ -11175,7 +11187,7 @@
     </row>
     <row r="28" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B28" s="9">
         <v>2015</v>
@@ -11185,7 +11197,7 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F28" s="8">
         <v>2015</v>
@@ -11194,7 +11206,7 @@
         <v>12193</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J28" s="8">
         <v>2015</v>
@@ -11203,7 +11215,7 @@
         <v>23724</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N28" s="8">
         <v>2015</v>
@@ -11214,7 +11226,7 @@
     </row>
     <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B29" s="9">
         <v>2014</v>
@@ -11223,7 +11235,7 @@
         <v>86833</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F29" s="8">
         <v>2014</v>
@@ -11232,7 +11244,7 @@
         <v>22074</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J29" s="8">
         <v>2014</v>
@@ -11241,7 +11253,7 @@
         <v>27017</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N29" s="8">
         <v>2014</v>
@@ -11252,7 +11264,7 @@
     </row>
     <row r="30" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" s="9">
         <v>2013</v>
@@ -11261,7 +11273,7 @@
         <v>77849</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F30" s="8">
         <v>2013</v>
@@ -11270,7 +11282,7 @@
         <v>21863</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J30" s="8">
         <v>2013</v>
@@ -11279,7 +11291,7 @@
         <v>24567</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N30" s="8">
         <v>2013</v>
@@ -11290,7 +11302,7 @@
     </row>
     <row r="31" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B31" s="8">
         <v>2012</v>
@@ -11300,7 +11312,7 @@
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F31" s="8">
         <v>2012</v>
@@ -11309,7 +11321,7 @@
         <v>16978</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J31" s="8">
         <v>2012</v>
@@ -11318,7 +11330,7 @@
         <v>29321</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N31" s="8">
         <v>2012</v>
@@ -11329,7 +11341,7 @@
     </row>
     <row r="32" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B32" s="8">
         <v>2011</v>
@@ -11339,7 +11351,7 @@
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F32" s="8">
         <v>2011</v>
@@ -11348,7 +11360,7 @@
         <v>23150</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J32" s="8">
         <v>2011</v>
@@ -11357,7 +11369,7 @@
         <v>24639</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N32" s="8">
         <v>2011</v>
@@ -11372,12 +11384,12 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="37" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B34" s="37"/>
       <c r="D34" s="8"/>
       <c r="E34" s="37" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F34" s="37"/>
       <c r="M34" s="16"/>
@@ -11385,7 +11397,7 @@
     </row>
     <row r="35" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>1</v>
@@ -11395,7 +11407,7 @@
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>1</v>
@@ -11408,7 +11420,7 @@
     </row>
     <row r="36" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B36" s="8">
         <v>2025</v>
@@ -11418,7 +11430,7 @@
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" s="16">
         <v>2025</v>
@@ -11431,7 +11443,7 @@
     </row>
     <row r="37" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B37" s="8">
         <v>2024</v>
@@ -11441,7 +11453,7 @@
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" s="16">
         <v>2024</v>
@@ -11454,7 +11466,7 @@
     </row>
     <row r="38" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B38" s="8">
         <v>2023</v>
@@ -11464,7 +11476,7 @@
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" s="16">
         <v>2023</v>
@@ -11477,7 +11489,7 @@
     </row>
     <row r="39" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B39" s="8">
         <v>2022</v>
@@ -11487,7 +11499,7 @@
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" s="16">
         <v>2022</v>
@@ -11500,7 +11512,7 @@
     </row>
     <row r="40" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B40" s="8">
         <v>2021</v>
@@ -11510,7 +11522,7 @@
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" s="16">
         <v>2021</v>
@@ -11523,7 +11535,7 @@
     </row>
     <row r="41" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B41" s="8">
         <v>2020</v>
@@ -11533,7 +11545,7 @@
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" s="16">
         <v>2020</v>
@@ -11546,7 +11558,7 @@
     </row>
     <row r="42" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B42" s="8">
         <v>2019</v>
@@ -11556,7 +11568,7 @@
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" s="16">
         <v>2019</v>
@@ -11569,7 +11581,7 @@
     </row>
     <row r="43" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B43" s="8">
         <v>2018</v>
@@ -11579,7 +11591,7 @@
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" s="16">
         <v>2018</v>
@@ -11592,7 +11604,7 @@
     </row>
     <row r="44" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B44" s="8">
         <v>2017</v>
@@ -11602,7 +11614,7 @@
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" s="16">
         <v>2017</v>
@@ -11615,7 +11627,7 @@
     </row>
     <row r="45" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B45" s="8">
         <v>2016</v>
@@ -11625,7 +11637,7 @@
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" s="16">
         <v>2016</v>
@@ -11638,7 +11650,7 @@
     </row>
     <row r="46" spans="1:14" ht="19" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B46" s="8">
         <v>2015</v>
@@ -11648,7 +11660,7 @@
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" s="16">
         <v>2015</v>
@@ -11661,7 +11673,7 @@
     </row>
     <row r="47" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B47" s="8">
         <v>2014</v>
@@ -11671,7 +11683,7 @@
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" s="16">
         <v>2014</v>
@@ -11684,7 +11696,7 @@
     </row>
     <row r="48" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B48" s="8">
         <v>2013</v>
@@ -11693,7 +11705,7 @@
         <v>123549</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" s="16">
         <v>2013</v>
@@ -11706,7 +11718,7 @@
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B49" s="8">
         <v>2012</v>
@@ -11715,7 +11727,7 @@
         <v>118210</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" s="16">
         <v>2012</v>
@@ -11728,7 +11740,7 @@
     </row>
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B50" s="8">
         <v>2011</v>
@@ -11737,7 +11749,7 @@
         <v>76615</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" s="16">
         <v>2011</v>
@@ -11750,7 +11762,7 @@
     </row>
     <row r="51" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B51" s="8">
         <v>2025</v>
@@ -11759,7 +11771,7 @@
         <v>238000</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F51" s="16">
         <v>2025</v>
@@ -11772,7 +11784,7 @@
     </row>
     <row r="52" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B52" s="8">
         <v>2024</v>
@@ -11781,7 +11793,7 @@
         <v>206000</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F52" s="16">
         <v>2024</v>
@@ -11794,7 +11806,7 @@
     </row>
     <row r="53" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B53" s="8">
         <v>2023</v>
@@ -11803,7 +11815,7 @@
         <v>167000</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F53" s="16">
         <v>2023</v>
@@ -11816,7 +11828,7 @@
     </row>
     <row r="54" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B54" s="8">
         <v>2022</v>
@@ -11825,7 +11837,7 @@
         <v>166500</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F54" s="16">
         <v>2022</v>
@@ -11838,7 +11850,7 @@
     </row>
     <row r="55" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B55" s="8">
         <v>2021</v>
@@ -11847,7 +11859,7 @@
         <v>141900</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F55" s="16">
         <v>2021</v>
@@ -11860,7 +11872,7 @@
     </row>
     <row r="56" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B56" s="8">
         <v>2020</v>
@@ -11869,7 +11881,7 @@
         <v>118300</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F56" s="16">
         <v>2020</v>
@@ -11882,7 +11894,7 @@
     </row>
     <row r="57" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B57" s="8">
         <v>2019</v>
@@ -11891,7 +11903,7 @@
         <v>102300</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F57" s="16">
         <v>2019</v>
@@ -11904,7 +11916,7 @@
     </row>
     <row r="58" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B58" s="8">
         <v>2018</v>
@@ -11913,7 +11925,7 @@
         <v>82700</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F58" s="16">
         <v>2018</v>
@@ -11926,7 +11938,7 @@
     </row>
     <row r="59" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B59" s="8">
         <v>2017</v>
@@ -11935,7 +11947,7 @@
         <v>72400</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F59" s="16">
         <v>2017</v>
@@ -11948,7 +11960,7 @@
     </row>
     <row r="60" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B60" s="8">
         <v>2016</v>
@@ -11957,7 +11969,7 @@
         <v>71900</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F60" s="16">
         <v>2016</v>
@@ -11970,7 +11982,7 @@
     </row>
     <row r="61" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B61" s="8">
         <v>2015</v>
@@ -11979,7 +11991,7 @@
         <v>80000</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F61" s="16">
         <v>2015</v>
@@ -11992,7 +12004,7 @@
     </row>
     <row r="62" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B62" s="8">
         <v>2014</v>
@@ -12001,7 +12013,7 @@
         <v>89700</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F62" s="16">
         <v>2014</v>
@@ -12014,7 +12026,7 @@
     </row>
     <row r="63" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B63" s="8">
         <v>2013</v>
@@ -12023,7 +12035,7 @@
         <v>78900</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F63" s="16">
         <v>2013</v>
@@ -12036,7 +12048,7 @@
     </row>
     <row r="64" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B64" s="8">
         <v>2012</v>
@@ -12045,7 +12057,7 @@
         <v>66500</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F64" s="16">
         <v>2012</v>
@@ -12058,7 +12070,7 @@
     </row>
     <row r="65" spans="1:12" ht="19" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B65" s="8">
         <v>2011</v>
@@ -12067,7 +12079,7 @@
         <v>57000</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F65" s="16">
         <v>2011</v>
@@ -12572,7 +12584,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -12587,21 +12599,21 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>2011</v>
@@ -12653,7 +12665,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>2012</v>
@@ -12705,7 +12717,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>2013</v>
@@ -12757,7 +12769,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>2014</v>
@@ -12809,7 +12821,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>2015</v>
@@ -12861,7 +12873,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>2016</v>
@@ -12913,7 +12925,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>2017</v>
@@ -12965,7 +12977,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>2018</v>
@@ -13017,7 +13029,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>2019</v>
@@ -13069,7 +13081,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>2020</v>
@@ -13121,7 +13133,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>2021</v>
@@ -13173,7 +13185,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>2022</v>
@@ -13225,7 +13237,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>2023</v>
@@ -13277,7 +13289,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>2024</v>
@@ -13329,7 +13341,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>2025</v>
@@ -13381,7 +13393,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>2011</v>
@@ -13433,7 +13445,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>2012</v>
@@ -13485,7 +13497,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>2013</v>
@@ -13537,7 +13549,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20">
         <v>2014</v>
@@ -13589,7 +13601,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>2015</v>
@@ -13641,7 +13653,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22">
         <v>2016</v>
@@ -13693,7 +13705,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23">
         <v>2017</v>
@@ -13745,7 +13757,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>2018</v>
@@ -13797,7 +13809,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B25">
         <v>2019</v>
@@ -13849,7 +13861,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26">
         <v>2020</v>
@@ -13901,7 +13913,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27">
         <v>2021</v>
@@ -13953,7 +13965,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B28">
         <v>2022</v>
@@ -14005,7 +14017,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B29">
         <v>2023</v>
@@ -14057,7 +14069,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30">
         <v>2024</v>
@@ -14109,7 +14121,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B31">
         <v>2025</v>
@@ -14192,42 +14204,42 @@
   <sheetData>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
         <v>15</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>17</v>
       </c>
-      <c r="H11" t="s">
-        <v>19</v>
-      </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -14622,7 +14634,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>4047960</v>
@@ -14634,7 +14646,7 @@
         <v>6121950</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G27" s="5">
         <v>0.23398097844429991</v>
@@ -14648,42 +14660,42 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>17</v>
       </c>
-      <c r="C30" t="s">
-        <v>19</v>
-      </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
         <v>15</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>17</v>
       </c>
-      <c r="H30" t="s">
-        <v>19</v>
-      </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
@@ -15078,7 +15090,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B46" s="5">
         <v>0.85004585802915866</v>
@@ -15090,7 +15102,7 @@
         <v>0.59471267638865533</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G46">
         <v>1054699</v>
@@ -15127,7 +15139,7 @@
   <sheetData>
     <row r="1" spans="1:19" s="6" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -15155,31 +15167,31 @@
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O10" s="31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P10" s="31" t="s">
         <v>1</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O11" s="32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P11" s="32">
         <v>2025</v>
       </c>
       <c r="Q11" s="33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28"/>
       <c r="B13" s="28"/>
       <c r="C13" s="28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
@@ -15193,13 +15205,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="27"/>
